--- a/docs/演示导入模板-合作成果.xlsx
+++ b/docs/演示导入模板-合作成果.xlsx
@@ -23,9 +23,10 @@
 * 必填列。
 成果类型：岗位成果 / 场景成果 / 课程成果 / 自定义成果（或 job / scene / course / custom），默认为 自定义成果
 成果日期：格式 YYYY-MM-DD，选填
-关联归属项目：项目名称，选填，多值用中文分号「；」分隔，需与系统「合作项目」中的项目名称一致
-关联合作企业：企业名称，选填，多值用中文分号「；」分隔，需与系统「合作企业」中的企业名称一致
-关联二级学院：学院名称，选填，多值用中文分号「；」分隔
+成果描述：文本，选填
+归属项目：项目名称，选填，多值用中文分号「；」分隔，需与系统「合作项目」中的项目名称一致（按名称自动关联）
+合作企业：企业名称，选填，多值用中文分号「；」分隔，需与系统「合作企业」中的企业名称一致（按名称自动关联）
+二级学院：学院名称，选填，多值用中文分号「；」分隔
 公开显示：是 / 否，选填，默认为 否</t>
   </si>
   <si>
@@ -35,19 +36,19 @@
     <t>成果类型</t>
   </si>
   <si>
-    <t>描述</t>
-  </si>
-  <si>
     <t>成果日期</t>
   </si>
   <si>
-    <t>关联归属项目</t>
-  </si>
-  <si>
-    <t>关联合作企业</t>
-  </si>
-  <si>
-    <t>关联二级学院</t>
+    <t>成果描述</t>
+  </si>
+  <si>
+    <t>归属项目</t>
+  </si>
+  <si>
+    <t>合作企业</t>
+  </si>
+  <si>
+    <t>二级学院</t>
   </si>
   <si>
     <t>公开显示</t>
@@ -59,12 +60,12 @@
     <t>自定义成果</t>
   </si>
   <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
     <t>校企联合制定充电桩检测与智能运维标准，涵盖安全检测、故障诊断与远程运维流程，已应用于企业售后体系并转化为教学案例。</t>
   </si>
   <si>
-    <t>2026-10-15</t>
-  </si>
-  <si>
     <t>新能源汽车充电桩联合研发项目</t>
   </si>
   <si>
@@ -83,12 +84,12 @@
     <t>课程成果</t>
   </si>
   <si>
+    <t>2026-12-20</t>
+  </si>
+  <si>
     <t>基于企业真实产线开发的数字化仿真实训课程，配套任务工单与考核标准，已纳入机电一体化专业核心课程。</t>
   </si>
   <si>
-    <t>2026-12-20</t>
-  </si>
-  <si>
     <t>智能制造实训基地共建项目</t>
   </si>
   <si>
@@ -101,10 +102,10 @@
     <t>场景成果</t>
   </si>
   <si>
+    <t>2027-01-10</t>
+  </si>
+  <si>
     <t>依托联合实验室建设的充电桩智能运维实践场景，覆盖设备调试、远程监控与故障处理全流程，支持岗位实训与技能竞赛。</t>
-  </si>
-  <si>
-    <t>2027-01-10</t>
   </si>
   <si>
     <t>否</t>
@@ -439,14 +440,14 @@
   <cols>
     <col customWidth="true" max="1" min="1" width="36"/>
     <col customWidth="true" max="2" min="2" width="22"/>
-    <col customWidth="true" max="3" min="3" width="50"/>
-    <col customWidth="true" max="4" min="4" width="16"/>
+    <col customWidth="true" max="3" min="3" width="16"/>
+    <col customWidth="true" max="4" min="4" width="50"/>
     <col customWidth="true" max="6" min="5" width="44"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="288" customHeight="true">
+    <row r="1" ht="320" customHeight="true">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
